--- a/artfynd/A 5134-2024 artfynd.xlsx
+++ b/artfynd/A 5134-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120487664</v>
+        <v>120487666</v>
       </c>
       <c r="B2" t="n">
         <v>79160</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436774</v>
+        <v>436799</v>
       </c>
       <c r="R2" t="n">
-        <v>6757994</v>
+        <v>6757961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120487702</v>
+        <v>120487829</v>
       </c>
       <c r="B3" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436866</v>
+        <v>436848</v>
       </c>
       <c r="R3" t="n">
-        <v>6757926</v>
+        <v>6757905</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120487799</v>
+        <v>120487919</v>
       </c>
       <c r="B4" t="n">
-        <v>8432</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,27 +895,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -924,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436847</v>
+        <v>436744</v>
       </c>
       <c r="R4" t="n">
-        <v>6757923</v>
+        <v>6757991</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120487663</v>
+        <v>120487669</v>
       </c>
       <c r="B5" t="n">
         <v>79160</v>
@@ -1026,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436764</v>
+        <v>436810</v>
       </c>
       <c r="R5" t="n">
-        <v>6757969</v>
+        <v>6757935</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120487919</v>
+        <v>120487668</v>
       </c>
       <c r="B6" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,47 +1104,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436744</v>
+        <v>436844</v>
       </c>
       <c r="R6" t="n">
-        <v>6757991</v>
+        <v>6757909</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1194,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120487662</v>
+        <v>120487915</v>
       </c>
       <c r="B7" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,38 +1206,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436745</v>
+        <v>436737</v>
       </c>
       <c r="R7" t="n">
-        <v>6757897</v>
+        <v>6757903</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120487796</v>
+        <v>120487663</v>
       </c>
       <c r="B8" t="n">
-        <v>8432</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,43 +1317,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436750</v>
+        <v>436764</v>
       </c>
       <c r="R8" t="n">
-        <v>6757932</v>
+        <v>6757969</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1408,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487918</v>
+        <v>120487927</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,47 +1419,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436745</v>
+        <v>436799</v>
       </c>
       <c r="R9" t="n">
-        <v>6757985</v>
+        <v>6757993</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487666</v>
+        <v>120487916</v>
       </c>
       <c r="B10" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1531,38 +1521,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436799</v>
+        <v>436752</v>
       </c>
       <c r="R10" t="n">
-        <v>6757961</v>
+        <v>6757945</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1723,7 +1722,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487668</v>
+        <v>120487665</v>
       </c>
       <c r="B12" t="n">
         <v>79160</v>
@@ -1763,10 +1762,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436844</v>
+        <v>436822</v>
       </c>
       <c r="R12" t="n">
-        <v>6757909</v>
+        <v>6757983</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1825,10 +1824,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120487665</v>
+        <v>120487921</v>
       </c>
       <c r="B13" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1837,28 +1836,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
@@ -1868,7 +1876,7 @@
         <v>436822</v>
       </c>
       <c r="R13" t="n">
-        <v>6757983</v>
+        <v>6757938</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,10 +1935,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487920</v>
+        <v>120487830</v>
       </c>
       <c r="B14" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1939,47 +1947,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436836</v>
+        <v>436865</v>
       </c>
       <c r="R14" t="n">
-        <v>6757957</v>
+        <v>6757925</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2038,10 +2037,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120487829</v>
+        <v>120487930</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2054,21 +2053,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2078,10 +2077,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436848</v>
+        <v>436771</v>
       </c>
       <c r="R15" t="n">
-        <v>6757905</v>
+        <v>6757882</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2140,10 +2139,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120487922</v>
+        <v>120487667</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2152,47 +2151,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436797</v>
+        <v>436838</v>
       </c>
       <c r="R16" t="n">
-        <v>6757935</v>
+        <v>6757954</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2251,10 +2241,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120487669</v>
+        <v>120487796</v>
       </c>
       <c r="B17" t="n">
-        <v>79160</v>
+        <v>8432</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2263,38 +2253,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436810</v>
+        <v>436750</v>
       </c>
       <c r="R17" t="n">
-        <v>6757935</v>
+        <v>6757932</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2353,10 +2348,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120487915</v>
+        <v>120487702</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>74654</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2365,47 +2360,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436737</v>
+        <v>436866</v>
       </c>
       <c r="R18" t="n">
-        <v>6757903</v>
+        <v>6757926</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,10 +2450,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487921</v>
+        <v>120487799</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>8432</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,31 +2466,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2513,10 +2495,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436822</v>
+        <v>436847</v>
       </c>
       <c r="R19" t="n">
-        <v>6757938</v>
+        <v>6757923</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2575,10 +2557,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487917</v>
+        <v>120487929</v>
       </c>
       <c r="B20" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,47 +2569,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436776</v>
+        <v>436865</v>
       </c>
       <c r="R20" t="n">
-        <v>6757950</v>
+        <v>6757909</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,7 +2659,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120487797</v>
+        <v>120487798</v>
       </c>
       <c r="B21" t="n">
         <v>8432</v>
@@ -2731,10 +2704,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436799</v>
+        <v>436810</v>
       </c>
       <c r="R21" t="n">
-        <v>6757990</v>
+        <v>6757960</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,10 +2766,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120487916</v>
+        <v>120487783</v>
       </c>
       <c r="B22" t="n">
-        <v>91858</v>
+        <v>5485</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2805,47 +2778,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>101410</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436752</v>
+        <v>436860</v>
       </c>
       <c r="R22" t="n">
-        <v>6757945</v>
+        <v>6757915</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2886,6 +2859,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2904,10 +2878,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120487783</v>
+        <v>120487920</v>
       </c>
       <c r="B23" t="n">
-        <v>5485</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2916,47 +2890,47 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436860</v>
+        <v>436836</v>
       </c>
       <c r="R23" t="n">
-        <v>6757915</v>
+        <v>6757957</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2997,7 +2971,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3016,10 +2989,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120487928</v>
+        <v>120487917</v>
       </c>
       <c r="B24" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3028,38 +3001,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436825</v>
+        <v>436776</v>
       </c>
       <c r="R24" t="n">
-        <v>6757998</v>
+        <v>6757950</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3118,10 +3100,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120487991</v>
+        <v>120487662</v>
       </c>
       <c r="B25" t="n">
-        <v>91852</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3134,21 +3116,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3158,10 +3140,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436781</v>
+        <v>436745</v>
       </c>
       <c r="R25" t="n">
-        <v>6757968</v>
+        <v>6757897</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3220,7 +3202,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120487930</v>
+        <v>120487925</v>
       </c>
       <c r="B26" t="n">
         <v>78187</v>
@@ -3260,10 +3242,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436771</v>
+        <v>436729</v>
       </c>
       <c r="R26" t="n">
-        <v>6757882</v>
+        <v>6757920</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3322,10 +3304,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120487927</v>
+        <v>120487922</v>
       </c>
       <c r="B27" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3334,38 +3316,47 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436799</v>
+        <v>436797</v>
       </c>
       <c r="R27" t="n">
-        <v>6757993</v>
+        <v>6757935</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3424,10 +3415,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120487929</v>
+        <v>120487918</v>
       </c>
       <c r="B28" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3436,38 +3427,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436865</v>
+        <v>436745</v>
       </c>
       <c r="R28" t="n">
-        <v>6757909</v>
+        <v>6757985</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3526,10 +3526,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120487667</v>
+        <v>120487991</v>
       </c>
       <c r="B29" t="n">
-        <v>79160</v>
+        <v>91852</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3542,21 +3542,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3566,10 +3566,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436838</v>
+        <v>436781</v>
       </c>
       <c r="R29" t="n">
-        <v>6757954</v>
+        <v>6757968</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3628,10 +3628,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120487925</v>
+        <v>120487671</v>
       </c>
       <c r="B30" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3644,21 +3644,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3668,10 +3668,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436729</v>
+        <v>436772</v>
       </c>
       <c r="R30" t="n">
-        <v>6757920</v>
+        <v>6757877</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3730,7 +3730,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120487798</v>
+        <v>120487791</v>
       </c>
       <c r="B31" t="n">
         <v>8432</v>
@@ -3766,7 +3766,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3775,10 +3775,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436810</v>
+        <v>436819</v>
       </c>
       <c r="R31" t="n">
-        <v>6757960</v>
+        <v>6757978</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,10 +3837,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120487671</v>
+        <v>120487797</v>
       </c>
       <c r="B32" t="n">
-        <v>79160</v>
+        <v>8432</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3849,38 +3849,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436772</v>
+        <v>436799</v>
       </c>
       <c r="R32" t="n">
-        <v>6757877</v>
+        <v>6757990</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,10 +4046,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120487791</v>
+        <v>120487928</v>
       </c>
       <c r="B34" t="n">
-        <v>8432</v>
+        <v>78187</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4053,43 +4058,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436819</v>
+        <v>436825</v>
       </c>
       <c r="R34" t="n">
-        <v>6757978</v>
+        <v>6757998</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120487830</v>
+        <v>120487664</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4164,21 +4164,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436865</v>
+        <v>436774</v>
       </c>
       <c r="R35" t="n">
-        <v>6757925</v>
+        <v>6757994</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 5134-2024 artfynd.xlsx
+++ b/artfynd/A 5134-2024 artfynd.xlsx
@@ -1620,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487831</v>
+        <v>120487665</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1636,21 +1636,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436857</v>
+        <v>436822</v>
       </c>
       <c r="R11" t="n">
-        <v>6757937</v>
+        <v>6757983</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,10 +1722,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487665</v>
+        <v>120487831</v>
       </c>
       <c r="B12" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1738,21 +1738,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1762,10 +1762,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436822</v>
+        <v>436857</v>
       </c>
       <c r="R12" t="n">
-        <v>6757983</v>
+        <v>6757937</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 5134-2024 artfynd.xlsx
+++ b/artfynd/A 5134-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120487666</v>
+        <v>120487669</v>
       </c>
       <c r="B2" t="n">
         <v>79160</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436799</v>
+        <v>436810</v>
       </c>
       <c r="R2" t="n">
-        <v>6757961</v>
+        <v>6757935</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120487829</v>
+        <v>120487671</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436848</v>
+        <v>436772</v>
       </c>
       <c r="R3" t="n">
-        <v>6757905</v>
+        <v>6757877</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120487919</v>
+        <v>120487663</v>
       </c>
       <c r="B4" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,47 +891,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436744</v>
+        <v>436764</v>
       </c>
       <c r="R4" t="n">
-        <v>6757991</v>
+        <v>6757969</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120487669</v>
+        <v>120487919</v>
       </c>
       <c r="B5" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,38 +993,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436810</v>
+        <v>436744</v>
       </c>
       <c r="R5" t="n">
-        <v>6757935</v>
+        <v>6757991</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,10 +1092,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120487668</v>
+        <v>120487917</v>
       </c>
       <c r="B6" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,38 +1104,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436844</v>
+        <v>436776</v>
       </c>
       <c r="R6" t="n">
-        <v>6757909</v>
+        <v>6757950</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120487915</v>
+        <v>120487929</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,47 +1215,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436737</v>
+        <v>436865</v>
       </c>
       <c r="R7" t="n">
-        <v>6757903</v>
+        <v>6757909</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120487663</v>
+        <v>120487928</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,21 +1321,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436764</v>
+        <v>436825</v>
       </c>
       <c r="R8" t="n">
-        <v>6757969</v>
+        <v>6757998</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487927</v>
+        <v>120487665</v>
       </c>
       <c r="B9" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436799</v>
+        <v>436822</v>
       </c>
       <c r="R9" t="n">
-        <v>6757993</v>
+        <v>6757983</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1620,10 +1620,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487665</v>
+        <v>120487918</v>
       </c>
       <c r="B11" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1632,38 +1632,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436822</v>
+        <v>436745</v>
       </c>
       <c r="R11" t="n">
-        <v>6757983</v>
+        <v>6757985</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1722,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487831</v>
+        <v>120487666</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1738,21 +1747,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1762,10 +1771,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436857</v>
+        <v>436799</v>
       </c>
       <c r="R12" t="n">
-        <v>6757937</v>
+        <v>6757961</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1833,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120487921</v>
+        <v>120487922</v>
       </c>
       <c r="B13" t="n">
         <v>91858</v>
@@ -1873,10 +1882,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436822</v>
+        <v>436797</v>
       </c>
       <c r="R13" t="n">
-        <v>6757938</v>
+        <v>6757935</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1935,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487830</v>
+        <v>120487829</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -1975,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436865</v>
+        <v>436848</v>
       </c>
       <c r="R14" t="n">
-        <v>6757925</v>
+        <v>6757905</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2037,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120487930</v>
+        <v>120487831</v>
       </c>
       <c r="B15" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2053,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2077,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436771</v>
+        <v>436857</v>
       </c>
       <c r="R15" t="n">
-        <v>6757882</v>
+        <v>6757937</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120487667</v>
+        <v>120487925</v>
       </c>
       <c r="B16" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2155,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2179,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436838</v>
+        <v>436729</v>
       </c>
       <c r="R16" t="n">
-        <v>6757954</v>
+        <v>6757920</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2241,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120487796</v>
+        <v>120487799</v>
       </c>
       <c r="B17" t="n">
         <v>8432</v>
@@ -2286,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436750</v>
+        <v>436847</v>
       </c>
       <c r="R17" t="n">
-        <v>6757932</v>
+        <v>6757923</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2348,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120487702</v>
+        <v>120487798</v>
       </c>
       <c r="B18" t="n">
-        <v>74654</v>
+        <v>8432</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2360,38 +2369,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>106545</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436866</v>
+        <v>436810</v>
       </c>
       <c r="R18" t="n">
-        <v>6757926</v>
+        <v>6757960</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2450,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487799</v>
+        <v>120487664</v>
       </c>
       <c r="B19" t="n">
-        <v>8432</v>
+        <v>79160</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2462,43 +2476,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436847</v>
+        <v>436774</v>
       </c>
       <c r="R19" t="n">
-        <v>6757923</v>
+        <v>6757994</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2557,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487929</v>
+        <v>120487667</v>
       </c>
       <c r="B20" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2573,21 +2582,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2597,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436865</v>
+        <v>436838</v>
       </c>
       <c r="R20" t="n">
-        <v>6757909</v>
+        <v>6757954</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2659,10 +2668,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120487798</v>
+        <v>120487991</v>
       </c>
       <c r="B21" t="n">
-        <v>8432</v>
+        <v>91852</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2671,43 +2680,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>4362</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436810</v>
+        <v>436781</v>
       </c>
       <c r="R21" t="n">
-        <v>6757960</v>
+        <v>6757968</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2766,10 +2770,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120487783</v>
+        <v>120487797</v>
       </c>
       <c r="B22" t="n">
-        <v>5485</v>
+        <v>8432</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2778,47 +2782,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101410</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436860</v>
+        <v>436799</v>
       </c>
       <c r="R22" t="n">
-        <v>6757915</v>
+        <v>6757990</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2859,7 +2859,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2878,10 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120487920</v>
+        <v>120487796</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>8432</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2894,31 +2893,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2927,10 +2922,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436836</v>
+        <v>436750</v>
       </c>
       <c r="R23" t="n">
-        <v>6757957</v>
+        <v>6757932</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2989,7 +2984,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120487917</v>
+        <v>120487920</v>
       </c>
       <c r="B24" t="n">
         <v>91858</v>
@@ -3038,10 +3033,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436776</v>
+        <v>436836</v>
       </c>
       <c r="R24" t="n">
-        <v>6757950</v>
+        <v>6757957</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3100,10 +3095,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120487662</v>
+        <v>120487927</v>
       </c>
       <c r="B25" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3116,21 +3111,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3140,10 +3135,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436745</v>
+        <v>436799</v>
       </c>
       <c r="R25" t="n">
-        <v>6757897</v>
+        <v>6757993</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3202,10 +3197,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120487925</v>
+        <v>120487830</v>
       </c>
       <c r="B26" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3218,21 +3213,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3242,10 +3237,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436729</v>
+        <v>436865</v>
       </c>
       <c r="R26" t="n">
-        <v>6757920</v>
+        <v>6757925</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3304,7 +3299,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120487922</v>
+        <v>120487915</v>
       </c>
       <c r="B27" t="n">
         <v>91858</v>
@@ -3353,10 +3348,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436797</v>
+        <v>436737</v>
       </c>
       <c r="R27" t="n">
-        <v>6757935</v>
+        <v>6757903</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3415,10 +3410,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120487918</v>
+        <v>120487930</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3427,47 +3422,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436745</v>
+        <v>436771</v>
       </c>
       <c r="R28" t="n">
-        <v>6757985</v>
+        <v>6757882</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3526,10 +3512,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120487991</v>
+        <v>120487921</v>
       </c>
       <c r="B29" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3538,38 +3524,47 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436781</v>
+        <v>436822</v>
       </c>
       <c r="R29" t="n">
-        <v>6757968</v>
+        <v>6757938</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3628,10 +3623,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120487671</v>
+        <v>120487791</v>
       </c>
       <c r="B30" t="n">
-        <v>79160</v>
+        <v>8432</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3640,38 +3635,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436772</v>
+        <v>436819</v>
       </c>
       <c r="R30" t="n">
-        <v>6757877</v>
+        <v>6757978</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3730,10 +3730,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120487791</v>
+        <v>120487926</v>
       </c>
       <c r="B31" t="n">
-        <v>8432</v>
+        <v>78187</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3742,43 +3742,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436819</v>
+        <v>436774</v>
       </c>
       <c r="R31" t="n">
-        <v>6757978</v>
+        <v>6757994</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3837,10 +3832,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120487797</v>
+        <v>120487702</v>
       </c>
       <c r="B32" t="n">
-        <v>8432</v>
+        <v>74654</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3849,43 +3844,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436799</v>
+        <v>436866</v>
       </c>
       <c r="R32" t="n">
-        <v>6757990</v>
+        <v>6757926</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3944,10 +3934,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120487926</v>
+        <v>120487668</v>
       </c>
       <c r="B33" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3960,21 +3950,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3984,10 +3974,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436774</v>
+        <v>436844</v>
       </c>
       <c r="R33" t="n">
-        <v>6757994</v>
+        <v>6757909</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4046,10 +4036,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120487928</v>
+        <v>120487783</v>
       </c>
       <c r="B34" t="n">
-        <v>78187</v>
+        <v>5485</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4062,34 +4052,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436825</v>
+        <v>436860</v>
       </c>
       <c r="R34" t="n">
-        <v>6757998</v>
+        <v>6757915</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4130,6 +4129,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120487664</v>
+        <v>120487662</v>
       </c>
       <c r="B35" t="n">
         <v>79160</v>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436774</v>
+        <v>436745</v>
       </c>
       <c r="R35" t="n">
-        <v>6757994</v>
+        <v>6757897</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4247,6 +4247,116 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120487753</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hagmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>436832</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6757991</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vänjan</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-18</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 5134-2024 artfynd.xlsx
+++ b/artfynd/A 5134-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120487669</v>
+        <v>120487930</v>
       </c>
       <c r="B2" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>436810</v>
+        <v>436771</v>
       </c>
       <c r="R2" t="n">
-        <v>6757935</v>
+        <v>6757882</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120487671</v>
+        <v>120487702</v>
       </c>
       <c r="B3" t="n">
-        <v>79160</v>
+        <v>74654</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>436772</v>
+        <v>436866</v>
       </c>
       <c r="R3" t="n">
-        <v>6757877</v>
+        <v>6757926</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120487663</v>
+        <v>120487799</v>
       </c>
       <c r="B4" t="n">
-        <v>79160</v>
+        <v>8432</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,38 +891,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>436764</v>
+        <v>436847</v>
       </c>
       <c r="R4" t="n">
-        <v>6757969</v>
+        <v>6757923</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120487919</v>
+        <v>120487791</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>8432</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,31 +1002,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1030,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>436744</v>
+        <v>436819</v>
       </c>
       <c r="R5" t="n">
-        <v>6757991</v>
+        <v>6757978</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120487917</v>
+        <v>120487915</v>
       </c>
       <c r="B6" t="n">
         <v>91858</v>
@@ -1141,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>436776</v>
+        <v>436737</v>
       </c>
       <c r="R6" t="n">
-        <v>6757950</v>
+        <v>6757903</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120487929</v>
+        <v>120487663</v>
       </c>
       <c r="B7" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,21 +1220,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>436865</v>
+        <v>436764</v>
       </c>
       <c r="R7" t="n">
-        <v>6757909</v>
+        <v>6757969</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120487928</v>
+        <v>120487831</v>
       </c>
       <c r="B8" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,21 +1322,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>436825</v>
+        <v>436857</v>
       </c>
       <c r="R8" t="n">
-        <v>6757998</v>
+        <v>6757937</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1408,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487665</v>
+        <v>120487662</v>
       </c>
       <c r="B9" t="n">
         <v>79160</v>
@@ -1447,10 +1448,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436822</v>
+        <v>436745</v>
       </c>
       <c r="R9" t="n">
-        <v>6757983</v>
+        <v>6757897</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1509,7 +1510,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487916</v>
+        <v>120487920</v>
       </c>
       <c r="B10" t="n">
         <v>91858</v>
@@ -1558,10 +1559,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436752</v>
+        <v>436836</v>
       </c>
       <c r="R10" t="n">
-        <v>6757945</v>
+        <v>6757957</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1620,10 +1621,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120487918</v>
+        <v>120487928</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1632,47 +1633,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>436745</v>
+        <v>436825</v>
       </c>
       <c r="R11" t="n">
-        <v>6757985</v>
+        <v>6757998</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1731,10 +1723,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120487666</v>
+        <v>120487929</v>
       </c>
       <c r="B12" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1747,21 +1739,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1771,10 +1763,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>436799</v>
+        <v>436865</v>
       </c>
       <c r="R12" t="n">
-        <v>6757961</v>
+        <v>6757909</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1833,10 +1825,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120487922</v>
+        <v>120487927</v>
       </c>
       <c r="B13" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,47 +1837,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>436797</v>
+        <v>436799</v>
       </c>
       <c r="R13" t="n">
-        <v>6757935</v>
+        <v>6757993</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1944,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487829</v>
+        <v>120487783</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>5485</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,34 +1943,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>101410</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436848</v>
+        <v>436860</v>
       </c>
       <c r="R14" t="n">
-        <v>6757905</v>
+        <v>6757915</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2028,6 +2020,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2046,10 +2039,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120487831</v>
+        <v>120487668</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2062,21 +2055,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2079,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436857</v>
+        <v>436844</v>
       </c>
       <c r="R15" t="n">
-        <v>6757937</v>
+        <v>6757909</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,10 +2141,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120487925</v>
+        <v>120487665</v>
       </c>
       <c r="B16" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2157,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2181,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436729</v>
+        <v>436822</v>
       </c>
       <c r="R16" t="n">
-        <v>6757920</v>
+        <v>6757983</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,10 +2243,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120487799</v>
+        <v>120487830</v>
       </c>
       <c r="B17" t="n">
-        <v>8432</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2262,43 +2255,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>436847</v>
+        <v>436865</v>
       </c>
       <c r="R17" t="n">
-        <v>6757923</v>
+        <v>6757925</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2357,7 +2345,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120487798</v>
+        <v>120487796</v>
       </c>
       <c r="B18" t="n">
         <v>8432</v>
@@ -2402,10 +2390,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>436810</v>
+        <v>436750</v>
       </c>
       <c r="R18" t="n">
-        <v>6757960</v>
+        <v>6757932</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2464,10 +2452,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120487664</v>
+        <v>120487797</v>
       </c>
       <c r="B19" t="n">
-        <v>79160</v>
+        <v>8432</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2476,38 +2464,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>436774</v>
+        <v>436799</v>
       </c>
       <c r="R19" t="n">
-        <v>6757994</v>
+        <v>6757990</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,10 +2559,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120487667</v>
+        <v>120487925</v>
       </c>
       <c r="B20" t="n">
-        <v>79160</v>
+        <v>78187</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,21 +2575,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2599,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>436838</v>
+        <v>436729</v>
       </c>
       <c r="R20" t="n">
-        <v>6757954</v>
+        <v>6757920</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2668,10 +2661,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120487991</v>
+        <v>120487671</v>
       </c>
       <c r="B21" t="n">
-        <v>91852</v>
+        <v>79160</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2684,21 +2677,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2708,10 +2701,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>436781</v>
+        <v>436772</v>
       </c>
       <c r="R21" t="n">
-        <v>6757968</v>
+        <v>6757877</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2770,10 +2763,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120487797</v>
+        <v>120487918</v>
       </c>
       <c r="B22" t="n">
-        <v>8432</v>
+        <v>91858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2786,27 +2779,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2815,10 +2812,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>436799</v>
+        <v>436745</v>
       </c>
       <c r="R22" t="n">
-        <v>6757990</v>
+        <v>6757985</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2877,10 +2874,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120487796</v>
+        <v>120487829</v>
       </c>
       <c r="B23" t="n">
-        <v>8432</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2889,43 +2886,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>436750</v>
+        <v>436848</v>
       </c>
       <c r="R23" t="n">
-        <v>6757932</v>
+        <v>6757905</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2984,7 +2976,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120487920</v>
+        <v>120487916</v>
       </c>
       <c r="B24" t="n">
         <v>91858</v>
@@ -3033,10 +3025,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436836</v>
+        <v>436752</v>
       </c>
       <c r="R24" t="n">
-        <v>6757957</v>
+        <v>6757945</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3095,10 +3087,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120487927</v>
+        <v>120487669</v>
       </c>
       <c r="B25" t="n">
-        <v>78187</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3111,21 +3103,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3135,10 +3127,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436799</v>
+        <v>436810</v>
       </c>
       <c r="R25" t="n">
-        <v>6757993</v>
+        <v>6757935</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3197,10 +3189,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120487830</v>
+        <v>120487926</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3213,21 +3205,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3237,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436865</v>
+        <v>436774</v>
       </c>
       <c r="R26" t="n">
-        <v>6757925</v>
+        <v>6757994</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3299,7 +3291,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120487915</v>
+        <v>120487921</v>
       </c>
       <c r="B27" t="n">
         <v>91858</v>
@@ -3348,10 +3340,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436737</v>
+        <v>436822</v>
       </c>
       <c r="R27" t="n">
-        <v>6757903</v>
+        <v>6757938</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,10 +3402,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120487930</v>
+        <v>120487919</v>
       </c>
       <c r="B28" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3422,38 +3414,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436771</v>
+        <v>436744</v>
       </c>
       <c r="R28" t="n">
-        <v>6757882</v>
+        <v>6757991</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3512,7 +3513,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120487921</v>
+        <v>120487922</v>
       </c>
       <c r="B29" t="n">
         <v>91858</v>
@@ -3561,10 +3562,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436822</v>
+        <v>436797</v>
       </c>
       <c r="R29" t="n">
-        <v>6757938</v>
+        <v>6757935</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3623,7 +3624,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120487791</v>
+        <v>120487798</v>
       </c>
       <c r="B30" t="n">
         <v>8432</v>
@@ -3659,7 +3660,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3668,10 +3669,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>436819</v>
+        <v>436810</v>
       </c>
       <c r="R30" t="n">
-        <v>6757978</v>
+        <v>6757960</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3730,10 +3731,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120487926</v>
+        <v>120487991</v>
       </c>
       <c r="B31" t="n">
-        <v>78187</v>
+        <v>91852</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3746,21 +3747,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3770,10 +3771,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>436774</v>
+        <v>436781</v>
       </c>
       <c r="R31" t="n">
-        <v>6757994</v>
+        <v>6757968</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3832,10 +3833,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120487702</v>
+        <v>120487667</v>
       </c>
       <c r="B32" t="n">
-        <v>74654</v>
+        <v>79160</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3848,21 +3849,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3872,10 +3873,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>436866</v>
+        <v>436838</v>
       </c>
       <c r="R32" t="n">
-        <v>6757926</v>
+        <v>6757954</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3934,7 +3935,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120487668</v>
+        <v>120487664</v>
       </c>
       <c r="B33" t="n">
         <v>79160</v>
@@ -3974,10 +3975,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>436844</v>
+        <v>436774</v>
       </c>
       <c r="R33" t="n">
-        <v>6757909</v>
+        <v>6757994</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4036,10 +4037,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120487783</v>
+        <v>120487917</v>
       </c>
       <c r="B34" t="n">
-        <v>5485</v>
+        <v>91858</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4048,47 +4049,47 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>101410</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>436860</v>
+        <v>436776</v>
       </c>
       <c r="R34" t="n">
-        <v>6757915</v>
+        <v>6757950</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4129,7 +4130,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120487662</v>
+        <v>120487666</v>
       </c>
       <c r="B35" t="n">
         <v>79160</v>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>436745</v>
+        <v>436799</v>
       </c>
       <c r="R35" t="n">
-        <v>6757897</v>
+        <v>6757961</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 5134-2024 artfynd.xlsx
+++ b/artfynd/A 5134-2024 artfynd.xlsx
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120487662</v>
+        <v>120487920</v>
       </c>
       <c r="B9" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,38 +1420,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>436745</v>
+        <v>436836</v>
       </c>
       <c r="R9" t="n">
-        <v>6757897</v>
+        <v>6757957</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1510,10 +1519,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120487920</v>
+        <v>120487662</v>
       </c>
       <c r="B10" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,47 +1531,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>436836</v>
+        <v>436745</v>
       </c>
       <c r="R10" t="n">
-        <v>6757957</v>
+        <v>6757897</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1927,10 +1927,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120487783</v>
+        <v>120487668</v>
       </c>
       <c r="B14" t="n">
-        <v>5485</v>
+        <v>79160</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,43 +1943,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101410</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>436860</v>
+        <v>436844</v>
       </c>
       <c r="R14" t="n">
-        <v>6757915</v>
+        <v>6757909</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2020,7 +2011,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2039,7 +2029,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120487668</v>
+        <v>120487665</v>
       </c>
       <c r="B15" t="n">
         <v>79160</v>
@@ -2079,10 +2069,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>436844</v>
+        <v>436822</v>
       </c>
       <c r="R15" t="n">
-        <v>6757909</v>
+        <v>6757983</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,10 +2131,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120487665</v>
+        <v>120487783</v>
       </c>
       <c r="B16" t="n">
-        <v>79160</v>
+        <v>5485</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2157,34 +2147,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>101410</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>436822</v>
+        <v>436860</v>
       </c>
       <c r="R16" t="n">
-        <v>6757983</v>
+        <v>6757915</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,6 +2224,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2976,10 +2976,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120487916</v>
+        <v>120487669</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2988,47 +2988,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>436752</v>
+        <v>436810</v>
       </c>
       <c r="R24" t="n">
-        <v>6757945</v>
+        <v>6757935</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3087,10 +3078,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120487669</v>
+        <v>120487916</v>
       </c>
       <c r="B25" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3099,38 +3090,47 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>436810</v>
+        <v>436752</v>
       </c>
       <c r="R25" t="n">
-        <v>6757935</v>
+        <v>6757945</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3189,10 +3189,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120487926</v>
+        <v>120487921</v>
       </c>
       <c r="B26" t="n">
-        <v>78187</v>
+        <v>91858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3201,38 +3201,47 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>436774</v>
+        <v>436822</v>
       </c>
       <c r="R26" t="n">
-        <v>6757994</v>
+        <v>6757938</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3291,7 +3300,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120487921</v>
+        <v>120487919</v>
       </c>
       <c r="B27" t="n">
         <v>91858</v>
@@ -3340,10 +3349,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>436822</v>
+        <v>436744</v>
       </c>
       <c r="R27" t="n">
-        <v>6757938</v>
+        <v>6757991</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3402,7 +3411,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120487919</v>
+        <v>120487922</v>
       </c>
       <c r="B28" t="n">
         <v>91858</v>
@@ -3451,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>436744</v>
+        <v>436797</v>
       </c>
       <c r="R28" t="n">
-        <v>6757991</v>
+        <v>6757935</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3513,10 +3522,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120487922</v>
+        <v>120487926</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
+        <v>78187</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,47 +3534,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hagmyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>436797</v>
+        <v>436774</v>
       </c>
       <c r="R29" t="n">
-        <v>6757935</v>
+        <v>6757994</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>

--- a/artfynd/A 5134-2024 artfynd.xlsx
+++ b/artfynd/A 5134-2024 artfynd.xlsx
@@ -4253,7 +4253,7 @@
         <v>120487753</v>
       </c>
       <c r="B36" t="n">
-        <v>57348</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 5134-2024 artfynd.xlsx
+++ b/artfynd/A 5134-2024 artfynd.xlsx
@@ -4253,7 +4253,7 @@
         <v>120487753</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
